--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/GEORGIA_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/GEORGIA_2019.xlsx
@@ -1219,7 +1219,7 @@
         <v>23</v>
       </c>
       <c r="D48">
-        <v>0.0009375891728832905</v>
+        <v>0.0009375891728832904</v>
       </c>
     </row>
     <row r="49">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C132">
@@ -3379,7 +3379,7 @@
         <v>244</v>
       </c>
       <c r="D168">
-        <v>0.009946598181892299</v>
+        <v>0.009946598181892301</v>
       </c>
     </row>
     <row r="169">
@@ -3631,7 +3631,7 @@
         <v>23</v>
       </c>
       <c r="D182">
-        <v>0.0009375891728832905</v>
+        <v>0.0009375891728832904</v>
       </c>
     </row>
     <row r="183">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C183">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C317">
@@ -6979,7 +6979,7 @@
         <v>24</v>
       </c>
       <c r="D368">
-        <v>0.0009783539195303901</v>
+        <v>0.0009783539195303899</v>
       </c>
     </row>
     <row r="369">
@@ -7141,7 +7141,7 @@
         <v>23</v>
       </c>
       <c r="D377">
-        <v>0.0009375891728832905</v>
+        <v>0.0009375891728832904</v>
       </c>
     </row>
     <row r="378">
@@ -8617,7 +8617,7 @@
         <v>24</v>
       </c>
       <c r="D459">
-        <v>0.0009783539195303901</v>
+        <v>0.0009783539195303899</v>
       </c>
     </row>
     <row r="460">
@@ -11335,7 +11335,7 @@
         <v>24</v>
       </c>
       <c r="D610">
-        <v>0.0009783539195303901</v>
+        <v>0.0009783539195303899</v>
       </c>
     </row>
     <row r="611">
@@ -11929,7 +11929,7 @@
         <v>23</v>
       </c>
       <c r="D643">
-        <v>0.0009375891728832905</v>
+        <v>0.0009375891728832904</v>
       </c>
     </row>
     <row r="644">
@@ -12109,7 +12109,7 @@
         <v>238</v>
       </c>
       <c r="D653">
-        <v>0.009702009702009701</v>
+        <v>0.0097020097020097</v>
       </c>
     </row>
     <row r="654">
@@ -13261,7 +13261,7 @@
         <v>23</v>
       </c>
       <c r="D717">
-        <v>0.0009375891728832905</v>
+        <v>0.0009375891728832904</v>
       </c>
     </row>
     <row r="718">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C762">
@@ -14143,7 +14143,7 @@
         <v>24</v>
       </c>
       <c r="D766">
-        <v>0.0009783539195303901</v>
+        <v>0.0009783539195303899</v>
       </c>
     </row>
     <row r="767">
@@ -14323,7 +14323,7 @@
         <v>24</v>
       </c>
       <c r="D776">
-        <v>0.0009783539195303901</v>
+        <v>0.0009783539195303899</v>
       </c>
     </row>
     <row r="777">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C883">
@@ -16260,7 +16260,7 @@
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C884">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C926">
@@ -18157,7 +18157,7 @@
         <v>24</v>
       </c>
       <c r="D989">
-        <v>0.0009783539195303901</v>
+        <v>0.0009783539195303899</v>
       </c>
     </row>
     <row r="990">
@@ -21955,7 +21955,7 @@
         <v>23</v>
       </c>
       <c r="D1200">
-        <v>0.0009375891728832905</v>
+        <v>0.0009375891728832904</v>
       </c>
     </row>
     <row r="1201">
@@ -22513,7 +22513,7 @@
         <v>23</v>
       </c>
       <c r="D1231">
-        <v>0.0009375891728832905</v>
+        <v>0.0009375891728832904</v>
       </c>
     </row>
     <row r="1232">
@@ -22945,7 +22945,7 @@
         <v>23</v>
       </c>
       <c r="D1255">
-        <v>0.0009375891728832905</v>
+        <v>0.0009375891728832904</v>
       </c>
     </row>
     <row r="1256">
@@ -28165,7 +28165,7 @@
         <v>23</v>
       </c>
       <c r="D1545">
-        <v>0.0009375891728832905</v>
+        <v>0.0009375891728832904</v>
       </c>
     </row>
     <row r="1546">
